--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Noah Wester, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Noah Wester</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
